--- a/docs/semantic_layer_config.xlsx
+++ b/docs/semantic_layer_config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="10410"/>
+    <workbookView windowWidth="24000" windowHeight="10410" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="业务域" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="200">
   <si>
     <t>domain_code</t>
   </si>
@@ -126,7 +126,41 @@
     <t>住院待遇</t>
   </si>
   <si>
-    <t>本次结算待遇分段计算：起付金额、起算日期、医保内金额、统筹支付/自付、大额支付/自付、个人应负。是待遇分解的核心对象。</t>
+    <r>
+      <t>本次结算待遇分段计算：起付金额、起算日期、医保内金额、统筹支付</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>自付、大额支付</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>自付、个人应付。是待遇分解的核心对象。</t>
+    </r>
   </si>
   <si>
     <t>yb_dyxxzy</t>
@@ -138,6 +172,9 @@
     <t>住院分段</t>
   </si>
   <si>
+    <t>本次结算待遇分段计算：起付金额、起算日期、医保内金额、统筹支付/自付、大额支付/自付、个人应付。是待遇分解的核心对象。</t>
+  </si>
+  <si>
     <t>yb_zyfdxx</t>
   </si>
   <si>
@@ -159,7 +196,57 @@
     <t>住院费用明细</t>
   </si>
   <si>
-    <t>住院费用明细项目：项目编码/名称、收费等级、特需标志、数量、金额（总/医保内/医保外）、自付比例、归因分类。是费用解释树的数据来源。</t>
+    <r>
+      <t>住院费用明细项目：项目编码</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>名称、收费等级、特需标志、数量、金额（总</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>医保内</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>医保外）、自付比例、归因分类。是费用解释树的数据来源。</t>
+    </r>
   </si>
   <si>
     <t>yb_zyfymx</t>
@@ -171,7 +258,57 @@
     <t>药品目录</t>
   </si>
   <si>
-    <t>药品/诊疗目录支付标准：住院限价(A_zyxj)、医保支付标准(MEDIC_L)。用于费用归因时判断限价影响。</t>
+    <r>
+      <t>药品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>诊疗目录支付标准：住院限价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(A_zyxj)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、医保支付标准</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(MEDIC_L)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。用于费用归因时判断限价影响。</t>
+    </r>
   </si>
   <si>
     <t>yb_ypzdml</t>
@@ -408,7 +545,57 @@
     <t>收费等级</t>
   </si>
   <si>
-    <t>1(甲)/2(乙)/3(丙)</t>
+    <r>
+      <t>1(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>甲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)/2(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>乙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)/3(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>丙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
   <si>
     <t>收费项目甲乙丙等级分类</t>
@@ -549,7 +736,177 @@
     <t>enum_map</t>
   </si>
   <si>
-    <t>3→城镇职工; 4→工伤保险; 31→离休统筹; 32→公疗医照; 33→征地超转; 91→居民-学生儿童; 92→居民-无保障老人; 93→居民-无业</t>
+    <r>
+      <t>3→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>城镇职工</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>; 4→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>工伤保险</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>; 31→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>离休统筹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>; 32→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>公疗医照</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>; 33→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>征地超转</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>; 91→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>居民</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>学生儿童</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>; 92→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>居民</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无保障老人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>; 93→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>居民</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无业</t>
+    </r>
   </si>
   <si>
     <t>SQL中CASE WHEN转义</t>
@@ -1342,7 +1699,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1375,10 +1732,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1758,7 +2118,7 @@
       <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="16" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="11" t="s">
@@ -1847,13 +2207,13 @@
       <c r="A2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="16" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E2" s="11" t="s">
@@ -1876,7 +2236,7 @@
       <c r="C3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="15" t="s">
         <v>25</v>
       </c>
       <c r="E3" s="13" t="s">
@@ -1893,13 +2253,13 @@
       <c r="A4" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="16" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="11" t="s">
@@ -1912,7 +2272,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" ht="38.25" spans="1:7">
       <c r="A5" s="12" t="s">
         <v>31</v>
       </c>
@@ -1922,28 +2282,30 @@
       <c r="C5" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="13"/>
+      <c r="D5" s="15" t="s">
+        <v>33</v>
+      </c>
       <c r="E5" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
     </row>
     <row r="6" ht="25.5" spans="1:7">
       <c r="A6" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>36</v>
+      <c r="D6" s="15" t="s">
+        <v>37</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6" s="13">
         <v>1</v>
@@ -1954,19 +2316,19 @@
     </row>
     <row r="7" ht="38.25" spans="1:7">
       <c r="A7" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="14" t="s">
         <v>39</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>40</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>40</v>
+      <c r="D7" s="16" t="s">
+        <v>41</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F7" s="11">
         <v>10</v>
@@ -1977,19 +2339,19 @@
     </row>
     <row r="8" ht="25.5" spans="1:7">
       <c r="A8" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>44</v>
+      <c r="D8" s="15" t="s">
+        <v>45</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F8" s="13">
         <v>2</v>
@@ -2025,7 +2387,7 @@
   <sheetData>
     <row r="1" ht="13.9" spans="1:9">
       <c r="A1" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>1</v>
@@ -2034,892 +2396,892 @@
         <v>16</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H1" s="9" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="11" t="s">
         <v>53</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>54</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>57</v>
+        <v>57</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>58</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" ht="51" spans="1:9">
       <c r="A3" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" ht="63.75" spans="1:9">
       <c r="A4" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>23</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>23</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>31</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>31</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>31</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>31</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>31</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>31</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>116</v>
+        <v>57</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>117</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="I20" s="11" t="s">
         <v>118</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="B21" s="13" t="s">
         <v>122</v>
       </c>
+      <c r="B21" s="15" t="s">
+        <v>123</v>
+      </c>
       <c r="C21" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>123</v>
+        <v>56</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>124</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="H21" s="13" t="s">
-        <v>124</v>
+        <v>57</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>125</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>128</v>
+        <v>57</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>129</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" ht="51" spans="1:9">
       <c r="A29" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -2949,808 +3311,808 @@
   <sheetData>
     <row r="1" ht="27.75" spans="1:8">
       <c r="A1" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>22</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" ht="38.25" spans="1:8">
       <c r="A3" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="G3" s="13" t="s">
         <v>170</v>
       </c>
+      <c r="G3" s="14" t="s">
+        <v>171</v>
+      </c>
       <c r="H3" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" ht="51" spans="1:8">
       <c r="A4" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>22</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G4" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>172</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>26</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>26</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>30</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" ht="25.5" spans="1:8">
       <c r="A11" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B11" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>87</v>
-      </c>
       <c r="E11" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B12" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>90</v>
-      </c>
       <c r="E12" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B13" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C13" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>96</v>
-      </c>
       <c r="E13" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B14" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>99</v>
-      </c>
       <c r="E14" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B15" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>102</v>
-      </c>
       <c r="E15" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B16" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>105</v>
-      </c>
       <c r="E16" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B17" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>108</v>
-      </c>
       <c r="E17" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B18" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>111</v>
-      </c>
       <c r="E18" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="B19" s="13" t="s">
         <v>115</v>
       </c>
+      <c r="B19" s="15" t="s">
+        <v>116</v>
+      </c>
       <c r="C19" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B20" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>118</v>
-      </c>
       <c r="E20" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B21" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>121</v>
-      </c>
       <c r="E21" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B22" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="C22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>125</v>
-      </c>
       <c r="E22" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B23" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>129</v>
-      </c>
       <c r="E23" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B25" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>134</v>
-      </c>
       <c r="E25" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B26" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="C26" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>137</v>
-      </c>
       <c r="E26" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B27" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>140</v>
-      </c>
       <c r="E27" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B28" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="C28" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>145</v>
-      </c>
       <c r="E28" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" ht="51" spans="1:8">
       <c r="A29" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B30" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="C30" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>153</v>
-      </c>
       <c r="E30" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B31" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>156</v>
-      </c>
       <c r="E31" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -3774,26 +4136,26 @@
   <sheetData>
     <row r="1" ht="17.6" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" ht="20.6" spans="1:4">
@@ -3812,28 +4174,28 @@
     </row>
     <row r="7" ht="13.85" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
